--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,36 +631,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>riya</t>
+          <t>sonali</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>99.99763280168271</v>
+        <v>99.99999999956984</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -670,36 +670,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>riya</t>
+          <t>shruti</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>99.99763280168271</v>
+        <v>99.99999999999946</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -709,79 +709,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sham</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>riya</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J8" t="n">
-        <v>99.99763280168271</v>
+        <v>0.10653150234293</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>High Placement Chance</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>sonali</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>89</v>
-      </c>
-      <c r="E9" t="n">
-        <v>90</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>85</v>
-      </c>
-      <c r="J9" t="n">
-        <v>99.99999999956984</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>High Placement Chance</t>
+          <t>Low Placement Chance</t>
         </is>
       </c>
     </row>
